--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="235">
   <si>
     <t>Profile</t>
   </si>
@@ -492,6 +492,9 @@
   </si>
   <si>
     <t>ONC Observation Codes#hygiene-needs</t>
+  </si>
+  <si>
+    <t>ONC Observation Codes#empathy-index</t>
   </si>
   <si>
     <t>onc-inspired-oxygen</t>
@@ -847,7 +850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:K109"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3582,28 +3585,28 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D79" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E79" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="B79" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="D79" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E79" t="s" s="2">
-        <v>162</v>
-      </c>
       <c r="F79" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>163</v>
+        <v>20</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>18</v>
@@ -3617,10 +3620,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C80" t="s" s="2">
         <v>75</v>
@@ -3629,7 +3632,7 @@
         <v>14</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F80" t="s" s="2">
         <v>14</v>
@@ -3638,7 +3641,7 @@
         <v>16</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>38</v>
+        <v>164</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>18</v>
@@ -3652,10 +3655,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C81" t="s" s="2">
         <v>75</v>
@@ -3664,7 +3667,7 @@
         <v>14</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F81" t="s" s="2">
         <v>14</v>
@@ -3687,10 +3690,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C82" t="s" s="2">
         <v>75</v>
@@ -3699,7 +3702,7 @@
         <v>14</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F82" t="s" s="2">
         <v>14</v>
@@ -3708,7 +3711,7 @@
         <v>16</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>18</v>
@@ -3722,10 +3725,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C83" t="s" s="2">
         <v>75</v>
@@ -3734,7 +3737,7 @@
         <v>14</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F83" t="s" s="2">
         <v>14</v>
@@ -3743,7 +3746,7 @@
         <v>16</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>18</v>
@@ -3757,10 +3760,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C84" t="s" s="2">
         <v>75</v>
@@ -3769,7 +3772,7 @@
         <v>14</v>
       </c>
       <c r="E84" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F84" t="s" s="2">
         <v>14</v>
@@ -3792,28 +3795,28 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>179</v>
+        <v>14</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="F85" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>18</v>
@@ -3827,10 +3830,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C86" t="s" s="2">
         <v>75</v>
@@ -3839,7 +3842,7 @@
         <v>14</v>
       </c>
       <c r="E86" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F86" t="s" s="2">
         <v>14</v>
@@ -3848,7 +3851,7 @@
         <v>16</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>18</v>
@@ -3862,28 +3865,28 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>14</v>
+        <v>180</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F87" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>18</v>
@@ -3897,28 +3900,28 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F88" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>18</v>
@@ -3935,7 +3938,7 @@
         <v>14</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C89" t="s" s="2">
         <v>14</v>
@@ -3944,7 +3947,7 @@
         <v>14</v>
       </c>
       <c r="E89" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F89" t="s" s="2">
         <v>14</v>
@@ -3967,28 +3970,28 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>188</v>
+        <v>14</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E90" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F90" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>18</v>
@@ -4002,28 +4005,28 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>191</v>
+        <v>14</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F91" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>18</v>
@@ -4037,10 +4040,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C92" t="s" s="2">
         <v>75</v>
@@ -4049,16 +4052,16 @@
         <v>14</v>
       </c>
       <c r="E92" t="s" s="2">
-        <v>14</v>
+        <v>191</v>
       </c>
       <c r="F92" t="s" s="2">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>18</v>
@@ -4072,10 +4075,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C93" t="s" s="2">
         <v>75</v>
@@ -4084,7 +4087,7 @@
         <v>14</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F93" t="s" s="2">
         <v>14</v>
@@ -4093,7 +4096,7 @@
         <v>16</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>18</v>
@@ -4107,10 +4110,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C94" t="s" s="2">
         <v>75</v>
@@ -4119,16 +4122,16 @@
         <v>14</v>
       </c>
       <c r="E94" t="s" s="2">
-        <v>202</v>
+        <v>14</v>
       </c>
       <c r="F94" t="s" s="2">
-        <v>14</v>
+        <v>197</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>38</v>
+        <v>117</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>18</v>
@@ -4142,10 +4145,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C95" t="s" s="2">
         <v>75</v>
@@ -4154,7 +4157,7 @@
         <v>14</v>
       </c>
       <c r="E95" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F95" t="s" s="2">
         <v>14</v>
@@ -4163,7 +4166,7 @@
         <v>16</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>18</v>
@@ -4177,28 +4180,28 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>206</v>
+        <v>14</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>14</v>
+        <v>160</v>
       </c>
       <c r="F96" t="s" s="2">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>209</v>
+        <v>14</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>18</v>
@@ -4212,10 +4215,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C97" t="s" s="2">
         <v>75</v>
@@ -4224,7 +4227,7 @@
         <v>14</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="F97" t="s" s="2">
         <v>14</v>
@@ -4233,7 +4236,7 @@
         <v>16</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>18</v>
@@ -4247,10 +4250,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="C98" t="s" s="2">
         <v>75</v>
@@ -4259,7 +4262,7 @@
         <v>14</v>
       </c>
       <c r="E98" t="s" s="2">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="F98" t="s" s="2">
         <v>14</v>
@@ -4268,7 +4271,7 @@
         <v>16</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>18</v>
@@ -4282,10 +4285,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="C99" t="s" s="2">
         <v>75</v>
@@ -4294,13 +4297,13 @@
         <v>14</v>
       </c>
       <c r="E99" t="s" s="2">
-        <v>218</v>
+        <v>14</v>
       </c>
       <c r="F99" t="s" s="2">
-        <v>14</v>
+        <v>209</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>16</v>
+        <v>210</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>17</v>
@@ -4317,10 +4320,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C100" t="s" s="2">
         <v>75</v>
@@ -4329,7 +4332,7 @@
         <v>14</v>
       </c>
       <c r="E100" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="F100" t="s" s="2">
         <v>14</v>
@@ -4338,7 +4341,7 @@
         <v>16</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>18</v>
@@ -4352,10 +4355,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C101" t="s" s="2">
         <v>75</v>
@@ -4364,7 +4367,7 @@
         <v>14</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="F101" t="s" s="2">
         <v>14</v>
@@ -4373,7 +4376,7 @@
         <v>16</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>18</v>
@@ -4387,10 +4390,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C102" t="s" s="2">
         <v>75</v>
@@ -4399,7 +4402,7 @@
         <v>14</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="F102" t="s" s="2">
         <v>14</v>
@@ -4422,10 +4425,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C103" t="s" s="2">
         <v>75</v>
@@ -4434,7 +4437,7 @@
         <v>14</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F103" t="s" s="2">
         <v>14</v>
@@ -4457,28 +4460,28 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>14</v>
+        <v>223</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F104" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>18</v>
@@ -4492,28 +4495,28 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>14</v>
+        <v>226</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E105" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F105" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>18</v>
@@ -4527,36 +4530,141 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>14</v>
+        <v>229</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E106" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="F106" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="C107" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D107" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E107" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="F107" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="C108" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D108" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E108" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="F106" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="H106" t="s" s="2">
+      <c r="F108" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H108" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K106" t="s" s="2">
+      <c r="I108" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="C109" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D109" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E109" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="F109" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K109" t="s" s="2">
         <v>14</v>
       </c>
     </row>

--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="244">
   <si>
     <t>Profile</t>
   </si>
@@ -353,7 +353,7 @@
     <t>Bladder Assessment</t>
   </si>
   <si>
-    <t>ONC Observation Codes#bladder-assessment</t>
+    <t>SNOMED CT#268390008</t>
   </si>
   <si>
     <t>onc-blood-pressure</t>
@@ -389,7 +389,7 @@
     <t>Bowel Assessment</t>
   </si>
   <si>
-    <t>ONC Observation Codes#bowel-assessment</t>
+    <t>SNOMED CT#268389004</t>
   </si>
   <si>
     <t>onc-braden-scale-assessment</t>
@@ -425,7 +425,7 @@
     <t>Catheter Care</t>
   </si>
   <si>
-    <t>ONC Observation Codes#catheter-care</t>
+    <t>SNOMED CT#226005007</t>
   </si>
   <si>
     <t>CodeableConceptĵ, stringĵ</t>
@@ -437,7 +437,7 @@
     <t>Continence Assessment</t>
   </si>
   <si>
-    <t>ONC Observation Codes#continence-assessment</t>
+    <t>SNOMED CT#417476007</t>
   </si>
   <si>
     <t>onc-dietary-requirements</t>
@@ -446,7 +446,16 @@
     <t>Dietary Requirements</t>
   </si>
   <si>
-    <t>ONC Observation Codes#dietary-requirements</t>
+    <t>SNOMED CT#116336009</t>
+  </si>
+  <si>
+    <t>onc-dressing-assessment</t>
+  </si>
+  <si>
+    <t>Dressing and Undressing Assessment</t>
+  </si>
+  <si>
+    <t>SNOMED CT#165235000</t>
   </si>
   <si>
     <t>onc-glasgow-coma-scale</t>
@@ -491,7 +500,7 @@
     <t>Personal Hygiene Needs Assessment</t>
   </si>
   <si>
-    <t>ONC Observation Codes#hygiene-needs</t>
+    <t>SNOMED CT#712552002</t>
   </si>
   <si>
     <t>ONC Observation Codes#empathy-index</t>
@@ -515,7 +524,7 @@
     <t>Medication Management Ability</t>
   </si>
   <si>
-    <t>ONC Observation Codes#medication-ability</t>
+    <t>SNOMED CT#285033005</t>
   </si>
   <si>
     <t>onc-medication-self-admin</t>
@@ -524,7 +533,7 @@
     <t>Medication Self-Administration Observation</t>
   </si>
   <si>
-    <t>ONC Observation Codes#medication-self-admin</t>
+    <t>SNOMED CT#225425006</t>
   </si>
   <si>
     <t>onc-mmse</t>
@@ -542,7 +551,7 @@
     <t>Mobility Assessment</t>
   </si>
   <si>
-    <t>ONC Observation Codes#mobility</t>
+    <t>SNOMED CT#82971005</t>
   </si>
   <si>
     <t>onc-monk-skintone-observation</t>
@@ -608,13 +617,25 @@
     <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1 (example)</t>
   </si>
   <si>
+    <t>onc-nursing-strength</t>
+  </si>
+  <si>
+    <t>ONC Nursing Strength</t>
+  </si>
+  <si>
+    <t>ONC Observation Codes#nursing-strengths</t>
+  </si>
+  <si>
+    <t>CodeableConcept, string</t>
+  </si>
+  <si>
     <t>onc-oral-care-assessment</t>
   </si>
   <si>
     <t>Oral Care Needs Assessment</t>
   </si>
   <si>
-    <t>ONC Observation Codes#oral-care</t>
+    <t>SNOMED CT#30175009</t>
   </si>
   <si>
     <t>onc-oral-intake-assessment</t>
@@ -623,7 +644,7 @@
     <t>Oral Intake Assessment</t>
   </si>
   <si>
-    <t>ONC Observation Codes#oral-intake</t>
+    <t>SNOMED CT#288852001</t>
   </si>
   <si>
     <t>onc-oxygen-saturation</t>
@@ -674,6 +695,15 @@
     <t>LOINC#9279-1</t>
   </si>
   <si>
+    <t>onc-skin-assessment</t>
+  </si>
+  <si>
+    <t>Skin Integrity Assessment</t>
+  </si>
+  <si>
+    <t>SNOMED CT#711041003</t>
+  </si>
+  <si>
     <t>onc-skintone-observation</t>
   </si>
   <si>
@@ -687,9 +717,6 @@
   </si>
   <si>
     <t>Swallowing Assessment</t>
-  </si>
-  <si>
-    <t>ONC Observation Codes#swallowing</t>
   </si>
   <si>
     <t>onc-waterlow-score</t>
@@ -850,7 +877,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K109"/>
+  <dimension ref="A1:K112"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3361,7 +3388,7 @@
         <v>16</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>18</v>
@@ -3375,28 +3402,28 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>14</v>
+        <v>148</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F73" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>18</v>
@@ -3413,7 +3440,7 @@
         <v>14</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C74" t="s" s="2">
         <v>14</v>
@@ -3422,7 +3449,7 @@
         <v>14</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F74" t="s" s="2">
         <v>14</v>
@@ -3448,7 +3475,7 @@
         <v>14</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C75" t="s" s="2">
         <v>14</v>
@@ -3457,7 +3484,7 @@
         <v>14</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F75" t="s" s="2">
         <v>14</v>
@@ -3480,10 +3507,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>151</v>
+        <v>14</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C76" t="s" s="2">
         <v>14</v>
@@ -3498,10 +3525,10 @@
         <v>14</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>18</v>
@@ -3521,7 +3548,7 @@
         <v>155</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>14</v>
@@ -3536,7 +3563,7 @@
         <v>16</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>18</v>
@@ -3571,7 +3598,7 @@
         <v>16</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>18</v>
@@ -3585,28 +3612,28 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>14</v>
+        <v>160</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F79" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>18</v>
@@ -3620,13 +3647,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B80" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="B80" t="s" s="2">
-        <v>162</v>
-      </c>
       <c r="C80" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>14</v>
@@ -3638,10 +3665,10 @@
         <v>14</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>18</v>
@@ -3655,10 +3682,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B81" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="C81" t="s" s="2">
         <v>75</v>
@@ -3667,16 +3694,16 @@
         <v>14</v>
       </c>
       <c r="E81" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="F81" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H81" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="F81" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>38</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>18</v>
@@ -3746,7 +3773,7 @@
         <v>16</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>18</v>
@@ -3781,7 +3808,7 @@
         <v>16</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>18</v>
@@ -3795,28 +3822,28 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>14</v>
+        <v>177</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="F85" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>18</v>
@@ -3830,28 +3857,28 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>177</v>
+        <v>14</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E86" t="s" s="2">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="F86" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>18</v>
@@ -3886,7 +3913,7 @@
         <v>16</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>18</v>
@@ -3935,28 +3962,28 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>14</v>
+        <v>186</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E89" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F89" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>18</v>
@@ -3973,7 +4000,7 @@
         <v>14</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C90" t="s" s="2">
         <v>14</v>
@@ -3982,7 +4009,7 @@
         <v>14</v>
       </c>
       <c r="E90" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F90" t="s" s="2">
         <v>14</v>
@@ -4008,7 +4035,7 @@
         <v>14</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C91" t="s" s="2">
         <v>14</v>
@@ -4017,7 +4044,7 @@
         <v>14</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F91" t="s" s="2">
         <v>14</v>
@@ -4040,13 +4067,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>189</v>
+        <v>14</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D92" t="s" s="2">
         <v>14</v>
@@ -4058,10 +4085,10 @@
         <v>14</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>18</v>
@@ -4122,16 +4149,16 @@
         <v>14</v>
       </c>
       <c r="E94" t="s" s="2">
-        <v>14</v>
+        <v>197</v>
       </c>
       <c r="F94" t="s" s="2">
-        <v>197</v>
+        <v>14</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>18</v>
@@ -4157,16 +4184,16 @@
         <v>14</v>
       </c>
       <c r="E95" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F95" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="F95" t="s" s="2">
-        <v>14</v>
-      </c>
       <c r="G95" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>38</v>
+        <v>117</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>18</v>
@@ -4180,10 +4207,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>14</v>
+        <v>201</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C96" t="s" s="2">
         <v>14</v>
@@ -4192,16 +4219,16 @@
         <v>14</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="F96" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>20</v>
+        <v>204</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>18</v>
@@ -4215,10 +4242,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C97" t="s" s="2">
         <v>75</v>
@@ -4227,7 +4254,7 @@
         <v>14</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F97" t="s" s="2">
         <v>14</v>
@@ -4250,28 +4277,28 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>204</v>
+        <v>14</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E98" t="s" s="2">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="F98" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>18</v>
@@ -4285,10 +4312,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C99" t="s" s="2">
         <v>75</v>
@@ -4297,16 +4324,16 @@
         <v>14</v>
       </c>
       <c r="E99" t="s" s="2">
-        <v>14</v>
+        <v>210</v>
       </c>
       <c r="F99" t="s" s="2">
-        <v>209</v>
+        <v>14</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>210</v>
+        <v>16</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>18</v>
@@ -4367,16 +4394,16 @@
         <v>14</v>
       </c>
       <c r="E101" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F101" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="F101" t="s" s="2">
-        <v>14</v>
-      </c>
       <c r="G101" t="s" s="2">
-        <v>16</v>
+        <v>217</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>18</v>
@@ -4390,10 +4417,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C102" t="s" s="2">
         <v>75</v>
@@ -4402,7 +4429,7 @@
         <v>14</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F102" t="s" s="2">
         <v>14</v>
@@ -4425,10 +4452,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C103" t="s" s="2">
         <v>75</v>
@@ -4437,7 +4464,7 @@
         <v>14</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F103" t="s" s="2">
         <v>14</v>
@@ -4446,7 +4473,7 @@
         <v>16</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>18</v>
@@ -4460,10 +4487,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C104" t="s" s="2">
         <v>75</v>
@@ -4472,7 +4499,7 @@
         <v>14</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F104" t="s" s="2">
         <v>14</v>
@@ -4481,7 +4508,7 @@
         <v>16</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>18</v>
@@ -4495,10 +4522,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C105" t="s" s="2">
         <v>75</v>
@@ -4507,7 +4534,7 @@
         <v>14</v>
       </c>
       <c r="E105" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F105" t="s" s="2">
         <v>14</v>
@@ -4516,7 +4543,7 @@
         <v>16</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>18</v>
@@ -4530,10 +4557,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C106" t="s" s="2">
         <v>75</v>
@@ -4542,7 +4569,7 @@
         <v>14</v>
       </c>
       <c r="E106" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F106" t="s" s="2">
         <v>14</v>
@@ -4565,28 +4592,28 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>14</v>
+        <v>233</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E107" t="s" s="2">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="F107" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>18</v>
@@ -4600,28 +4627,28 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>14</v>
+        <v>235</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E108" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="F108" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>18</v>
@@ -4635,36 +4662,141 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>14</v>
+        <v>238</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E109" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="F109" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H109" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="C110" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D110" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E110" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="F110" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H110" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I109" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K109" t="s" s="2">
+      <c r="I110" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D111" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E111" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="F111" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="C112" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D112" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E112" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="F112" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K112" t="s" s="2">
         <v>14</v>
       </c>
     </row>

--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -149,6 +149,102 @@
     <t>ONC Observation Codes#abc-intensity</t>
   </si>
   <si>
+    <t>onc-acvpu</t>
+  </si>
+  <si>
+    <t>ACVPU Consciousness Level</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#survey</t>
+  </si>
+  <si>
+    <t>SNOMED CT#1104441000000107</t>
+  </si>
+  <si>
+    <t>onc-barthel-index</t>
+  </si>
+  <si>
+    <t>Barthel Index</t>
+  </si>
+  <si>
+    <t>ONC Observation Codes#barthel-score</t>
+  </si>
+  <si>
+    <t>onc-bladder-assessment</t>
+  </si>
+  <si>
+    <t>Bladder Assessment</t>
+  </si>
+  <si>
+    <t>SNOMED CT#268390008</t>
+  </si>
+  <si>
+    <t>onc-blood-pressure</t>
+  </si>
+  <si>
+    <t>Blood Pressure</t>
+  </si>
+  <si>
+    <t>LOINC#85354-9</t>
+  </si>
+  <si>
+    <t>Quantityĵ, CodeableConceptĵ, stringĵ</t>
+  </si>
+  <si>
+    <t>LOINC#8480-6</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>LOINC#8462-4</t>
+  </si>
+  <si>
+    <t>onc-body-temperature</t>
+  </si>
+  <si>
+    <t>Body Temperature</t>
+  </si>
+  <si>
+    <t>LOINC#8310-5</t>
+  </si>
+  <si>
+    <t>onc-bowel-assessment</t>
+  </si>
+  <si>
+    <t>Bowel Assessment</t>
+  </si>
+  <si>
+    <t>SNOMED CT#268389004</t>
+  </si>
+  <si>
+    <t>onc-braden-scale-assessment</t>
+  </si>
+  <si>
+    <t>Braden Scale Assessment</t>
+  </si>
+  <si>
+    <t>ONC Observation Codes#braden-total-score</t>
+  </si>
+  <si>
+    <t>ONC Observation Codes#braden-sensory</t>
+  </si>
+  <si>
+    <t>ONC Observation Codes#braden-moisture</t>
+  </si>
+  <si>
+    <t>ONC Observation Codes#braden-activity</t>
+  </si>
+  <si>
+    <t>ONC Observation Codes#braden-mobility</t>
+  </si>
+  <si>
+    <t>ONC Observation Codes#braden-nutrition</t>
+  </si>
+  <si>
+    <t>ONC Observation Codes#braden-friction</t>
+  </si>
+  <si>
     <t>onc-bristol-stool-chart</t>
   </si>
   <si>
@@ -158,6 +254,18 @@
     <t>ONC Observation Codes#bristol-score</t>
   </si>
   <si>
+    <t>onc-catheter-care</t>
+  </si>
+  <si>
+    <t>Catheter Care</t>
+  </si>
+  <si>
+    <t>SNOMED CT#226005007</t>
+  </si>
+  <si>
+    <t>CodeableConceptĵ, stringĵ</t>
+  </si>
+  <si>
     <t>onc-clinical-frailty-scale</t>
   </si>
   <si>
@@ -167,6 +275,33 @@
     <t>ONC Observation Codes#cfs-score</t>
   </si>
   <si>
+    <t>onc-continence-assessment</t>
+  </si>
+  <si>
+    <t>Continence Assessment</t>
+  </si>
+  <si>
+    <t>SNOMED CT#417476007</t>
+  </si>
+  <si>
+    <t>onc-dietary-requirements</t>
+  </si>
+  <si>
+    <t>Dietary Requirements</t>
+  </si>
+  <si>
+    <t>SNOMED CT#116336009</t>
+  </si>
+  <si>
+    <t>onc-dressing-assessment</t>
+  </si>
+  <si>
+    <t>Dressing and Undressing Assessment</t>
+  </si>
+  <si>
+    <t>SNOMED CT#165235000</t>
+  </si>
+  <si>
     <t>onc-fluid-balance</t>
   </si>
   <si>
@@ -185,6 +320,84 @@
     <t>ONC Observation Codes#urine-output</t>
   </si>
   <si>
+    <t>onc-glasgow-coma-scale</t>
+  </si>
+  <si>
+    <t>Glasgow Coma Scale</t>
+  </si>
+  <si>
+    <t>LOINC#9269-2</t>
+  </si>
+  <si>
+    <t>LOINC#9267-6</t>
+  </si>
+  <si>
+    <t>LOINC#9270-0</t>
+  </si>
+  <si>
+    <t>LOINC#9268-4</t>
+  </si>
+  <si>
+    <t>onc-goal-evaluation</t>
+  </si>
+  <si>
+    <t>ONC Goal Evaluation</t>
+  </si>
+  <si>
+    <t>SNOMED CT#390906007</t>
+  </si>
+  <si>
+    <t>onc-heart-rate</t>
+  </si>
+  <si>
+    <t>Heart Rate</t>
+  </si>
+  <si>
+    <t>LOINC#8867-4</t>
+  </si>
+  <si>
+    <t>onc-hygiene-assessment</t>
+  </si>
+  <si>
+    <t>Personal Hygiene Needs Assessment</t>
+  </si>
+  <si>
+    <t>SNOMED CT#712552002</t>
+  </si>
+  <si>
+    <t>ONC Observation Codes#empathy-index</t>
+  </si>
+  <si>
+    <t>onc-inspired-oxygen</t>
+  </si>
+  <si>
+    <t>Inspired Oxygen</t>
+  </si>
+  <si>
+    <t>LOINC#3151-8</t>
+  </si>
+  <si>
+    <t>Quantityĵ, CodeableConceptĵ</t>
+  </si>
+  <si>
+    <t>onc-medication-ability</t>
+  </si>
+  <si>
+    <t>Medication Management Ability</t>
+  </si>
+  <si>
+    <t>SNOMED CT#285033005</t>
+  </si>
+  <si>
+    <t>onc-medication-self-admin</t>
+  </si>
+  <si>
+    <t>Medication Self-Administration Observation</t>
+  </si>
+  <si>
+    <t>SNOMED CT#225425006</t>
+  </si>
+  <si>
     <t>onc-mental-capacity</t>
   </si>
   <si>
@@ -194,6 +407,108 @@
     <t>ONC Observation Codes#mca-assessment</t>
   </si>
   <si>
+    <t>onc-mmse</t>
+  </si>
+  <si>
+    <t>Mini Mental State Examination (MMSE)</t>
+  </si>
+  <si>
+    <t>LOINC#72106-8</t>
+  </si>
+  <si>
+    <t>onc-mobility-assessment</t>
+  </si>
+  <si>
+    <t>Mobility Assessment</t>
+  </si>
+  <si>
+    <t>SNOMED CT#82971005</t>
+  </si>
+  <si>
+    <t>onc-monk-skintone-observation</t>
+  </si>
+  <si>
+    <t>Monk Skin Tone Observation</t>
+  </si>
+  <si>
+    <t>ONC Observation Codes#mst-score</t>
+  </si>
+  <si>
+    <t>onc-morse-fall-scale</t>
+  </si>
+  <si>
+    <t>Morse Fall Scale</t>
+  </si>
+  <si>
+    <t>LOINC#73830-2</t>
+  </si>
+  <si>
+    <t>onc-must-score</t>
+  </si>
+  <si>
+    <t>MUST Score (Malnutrition Universal Screening Tool)</t>
+  </si>
+  <si>
+    <t>ONC Observation Codes#must-score</t>
+  </si>
+  <si>
+    <t>ONC Observation Codes#must-bmi-score</t>
+  </si>
+  <si>
+    <t>ONC Observation Codes#must-weight-loss-score</t>
+  </si>
+  <si>
+    <t>ONC Observation Codes#must-acute-disease-score</t>
+  </si>
+  <si>
+    <t>onc-news2-score</t>
+  </si>
+  <si>
+    <t>NEWS2 Score</t>
+  </si>
+  <si>
+    <t>ONC Observation Codes#news2-score</t>
+  </si>
+  <si>
+    <t>onc-news2-subscore</t>
+  </si>
+  <si>
+    <t>NEWS2 Sub-Score</t>
+  </si>
+  <si>
+    <t>ONC Observation Codes#news2-subscore</t>
+  </si>
+  <si>
+    <t>onc-nursing-assessment</t>
+  </si>
+  <si>
+    <t>Open Nursing Core Assessment</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1 (example)</t>
+  </si>
+  <si>
+    <t>onc-nursing-strength</t>
+  </si>
+  <si>
+    <t>ONC Nursing Strength</t>
+  </si>
+  <si>
+    <t>ONC Observation Codes#nursing-strengths</t>
+  </si>
+  <si>
+    <t>CodeableConcept, string</t>
+  </si>
+  <si>
+    <t>onc-oral-care-assessment</t>
+  </si>
+  <si>
+    <t>Oral Care Needs Assessment</t>
+  </si>
+  <si>
+    <t>SNOMED CT#30175009</t>
+  </si>
+  <si>
     <t>onc-oral-health</t>
   </si>
   <si>
@@ -221,6 +536,36 @@
     <t>ONC Observation Codes#oral-saliva</t>
   </si>
   <si>
+    <t>onc-oral-intake-assessment</t>
+  </si>
+  <si>
+    <t>Oral Intake Assessment</t>
+  </si>
+  <si>
+    <t>SNOMED CT#288852001</t>
+  </si>
+  <si>
+    <t>onc-oxygen-saturation</t>
+  </si>
+  <si>
+    <t>Oxygen Saturation</t>
+  </si>
+  <si>
+    <t>LOINC#59408-5</t>
+  </si>
+  <si>
+    <t>onc-pain-assessment</t>
+  </si>
+  <si>
+    <t>Pain Assessment (NRS 0-10)</t>
+  </si>
+  <si>
+    <t>https://opennursingcoreig.com/ValueSet/pain-assessment-code-vs (required)</t>
+  </si>
+  <si>
+    <t>dateTime</t>
+  </si>
+  <si>
     <t>onc-patient-story</t>
   </si>
   <si>
@@ -233,18 +578,42 @@
     <t>ONC Observation Codes#patient-story</t>
   </si>
   <si>
+    <t>onc-qsofa</t>
+  </si>
+  <si>
+    <t>qSOFA (Quick SOFA)</t>
+  </si>
+  <si>
+    <t>LOINC#96790-1</t>
+  </si>
+  <si>
+    <t>onc-reasonable-adjustment</t>
+  </si>
+  <si>
+    <t>Reasonable Adjustment</t>
+  </si>
+  <si>
+    <t>ONC Observation Codes#reasonable-adjustment</t>
+  </si>
+  <si>
     <t>onc-relational-observation</t>
   </si>
   <si>
     <t>Relational Engagement Score</t>
   </si>
   <si>
-    <t>Observation Category Codes#survey</t>
-  </si>
-  <si>
     <t>ONC Observation Codes#relational-engagement</t>
   </si>
   <si>
+    <t>onc-respiration-rate</t>
+  </si>
+  <si>
+    <t>Respiration Rate</t>
+  </si>
+  <si>
+    <t>LOINC#9279-1</t>
+  </si>
+  <si>
     <t>onc-seizure-record</t>
   </si>
   <si>
@@ -260,15 +629,30 @@
     <t>ONC Observation Codes#seizure-duration</t>
   </si>
   <si>
-    <t>Quantity</t>
-  </si>
-  <si>
     <t>ONC Observation Codes#seizure-recovery</t>
   </si>
   <si>
     <t>ONC Observation Codes#seizure-trigger</t>
   </si>
   <si>
+    <t>onc-skin-assessment</t>
+  </si>
+  <si>
+    <t>Skin Integrity Assessment</t>
+  </si>
+  <si>
+    <t>SNOMED CT#711041003</t>
+  </si>
+  <si>
+    <t>onc-skintone-observation</t>
+  </si>
+  <si>
+    <t>Skin Tone Observation</t>
+  </si>
+  <si>
+    <t>LOINC#66555-4</t>
+  </si>
+  <si>
     <t>onc-sleep-pattern</t>
   </si>
   <si>
@@ -287,6 +671,12 @@
     <t>ONC Observation Codes#sleep-disturbances</t>
   </si>
   <si>
+    <t>onc-swallowing-assessment</t>
+  </si>
+  <si>
+    <t>Swallowing Assessment</t>
+  </si>
+  <si>
     <t>onc-urinalysis</t>
   </si>
   <si>
@@ -320,6 +710,15 @@
     <t>ONC Observation Codes#ua-sg</t>
   </si>
   <si>
+    <t>onc-waterlow-score</t>
+  </si>
+  <si>
+    <t>Waterlow Score</t>
+  </si>
+  <si>
+    <t>ONC Observation Codes#waterlow-score</t>
+  </si>
+  <si>
     <t>onc-what-matters</t>
   </si>
   <si>
@@ -327,405 +726,6 @@
   </si>
   <si>
     <t>ONC Observation Codes#what-matters</t>
-  </si>
-  <si>
-    <t>onc-acvpu</t>
-  </si>
-  <si>
-    <t>ACVPU Consciousness Level</t>
-  </si>
-  <si>
-    <t>SNOMED CT#1104441000000107</t>
-  </si>
-  <si>
-    <t>onc-barthel-index</t>
-  </si>
-  <si>
-    <t>Barthel Index</t>
-  </si>
-  <si>
-    <t>ONC Observation Codes#barthel-score</t>
-  </si>
-  <si>
-    <t>onc-bladder-assessment</t>
-  </si>
-  <si>
-    <t>Bladder Assessment</t>
-  </si>
-  <si>
-    <t>SNOMED CT#268390008</t>
-  </si>
-  <si>
-    <t>onc-blood-pressure</t>
-  </si>
-  <si>
-    <t>Blood Pressure</t>
-  </si>
-  <si>
-    <t>LOINC#85354-9</t>
-  </si>
-  <si>
-    <t>Quantityĵ, CodeableConceptĵ, stringĵ</t>
-  </si>
-  <si>
-    <t>LOINC#8480-6</t>
-  </si>
-  <si>
-    <t>LOINC#8462-4</t>
-  </si>
-  <si>
-    <t>onc-body-temperature</t>
-  </si>
-  <si>
-    <t>Body Temperature</t>
-  </si>
-  <si>
-    <t>LOINC#8310-5</t>
-  </si>
-  <si>
-    <t>onc-bowel-assessment</t>
-  </si>
-  <si>
-    <t>Bowel Assessment</t>
-  </si>
-  <si>
-    <t>SNOMED CT#268389004</t>
-  </si>
-  <si>
-    <t>onc-braden-scale-assessment</t>
-  </si>
-  <si>
-    <t>Braden Scale Assessment</t>
-  </si>
-  <si>
-    <t>ONC Observation Codes#braden-total-score</t>
-  </si>
-  <si>
-    <t>ONC Observation Codes#braden-sensory</t>
-  </si>
-  <si>
-    <t>ONC Observation Codes#braden-moisture</t>
-  </si>
-  <si>
-    <t>ONC Observation Codes#braden-activity</t>
-  </si>
-  <si>
-    <t>ONC Observation Codes#braden-mobility</t>
-  </si>
-  <si>
-    <t>ONC Observation Codes#braden-nutrition</t>
-  </si>
-  <si>
-    <t>ONC Observation Codes#braden-friction</t>
-  </si>
-  <si>
-    <t>onc-catheter-care</t>
-  </si>
-  <si>
-    <t>Catheter Care</t>
-  </si>
-  <si>
-    <t>SNOMED CT#226005007</t>
-  </si>
-  <si>
-    <t>CodeableConceptĵ, stringĵ</t>
-  </si>
-  <si>
-    <t>onc-continence-assessment</t>
-  </si>
-  <si>
-    <t>Continence Assessment</t>
-  </si>
-  <si>
-    <t>SNOMED CT#417476007</t>
-  </si>
-  <si>
-    <t>onc-dietary-requirements</t>
-  </si>
-  <si>
-    <t>Dietary Requirements</t>
-  </si>
-  <si>
-    <t>SNOMED CT#116336009</t>
-  </si>
-  <si>
-    <t>onc-dressing-assessment</t>
-  </si>
-  <si>
-    <t>Dressing and Undressing Assessment</t>
-  </si>
-  <si>
-    <t>SNOMED CT#165235000</t>
-  </si>
-  <si>
-    <t>onc-glasgow-coma-scale</t>
-  </si>
-  <si>
-    <t>Glasgow Coma Scale</t>
-  </si>
-  <si>
-    <t>LOINC#9269-2</t>
-  </si>
-  <si>
-    <t>LOINC#9267-6</t>
-  </si>
-  <si>
-    <t>LOINC#9270-0</t>
-  </si>
-  <si>
-    <t>LOINC#9268-4</t>
-  </si>
-  <si>
-    <t>onc-goal-evaluation</t>
-  </si>
-  <si>
-    <t>ONC Goal Evaluation</t>
-  </si>
-  <si>
-    <t>SNOMED CT#390906007</t>
-  </si>
-  <si>
-    <t>onc-heart-rate</t>
-  </si>
-  <si>
-    <t>Heart Rate</t>
-  </si>
-  <si>
-    <t>LOINC#8867-4</t>
-  </si>
-  <si>
-    <t>onc-hygiene-assessment</t>
-  </si>
-  <si>
-    <t>Personal Hygiene Needs Assessment</t>
-  </si>
-  <si>
-    <t>SNOMED CT#712552002</t>
-  </si>
-  <si>
-    <t>ONC Observation Codes#empathy-index</t>
-  </si>
-  <si>
-    <t>onc-inspired-oxygen</t>
-  </si>
-  <si>
-    <t>Inspired Oxygen</t>
-  </si>
-  <si>
-    <t>LOINC#3151-8</t>
-  </si>
-  <si>
-    <t>Quantityĵ, CodeableConceptĵ</t>
-  </si>
-  <si>
-    <t>onc-medication-ability</t>
-  </si>
-  <si>
-    <t>Medication Management Ability</t>
-  </si>
-  <si>
-    <t>SNOMED CT#285033005</t>
-  </si>
-  <si>
-    <t>onc-medication-self-admin</t>
-  </si>
-  <si>
-    <t>Medication Self-Administration Observation</t>
-  </si>
-  <si>
-    <t>SNOMED CT#225425006</t>
-  </si>
-  <si>
-    <t>onc-mmse</t>
-  </si>
-  <si>
-    <t>Mini Mental State Examination (MMSE)</t>
-  </si>
-  <si>
-    <t>LOINC#72106-8</t>
-  </si>
-  <si>
-    <t>onc-mobility-assessment</t>
-  </si>
-  <si>
-    <t>Mobility Assessment</t>
-  </si>
-  <si>
-    <t>SNOMED CT#82971005</t>
-  </si>
-  <si>
-    <t>onc-monk-skintone-observation</t>
-  </si>
-  <si>
-    <t>Monk Skin Tone Observation</t>
-  </si>
-  <si>
-    <t>ONC Observation Codes#mst-score</t>
-  </si>
-  <si>
-    <t>onc-morse-fall-scale</t>
-  </si>
-  <si>
-    <t>Morse Fall Scale</t>
-  </si>
-  <si>
-    <t>LOINC#73830-2</t>
-  </si>
-  <si>
-    <t>onc-must-score</t>
-  </si>
-  <si>
-    <t>MUST Score (Malnutrition Universal Screening Tool)</t>
-  </si>
-  <si>
-    <t>ONC Observation Codes#must-score</t>
-  </si>
-  <si>
-    <t>ONC Observation Codes#must-bmi-score</t>
-  </si>
-  <si>
-    <t>ONC Observation Codes#must-weight-loss-score</t>
-  </si>
-  <si>
-    <t>ONC Observation Codes#must-acute-disease-score</t>
-  </si>
-  <si>
-    <t>onc-news2-score</t>
-  </si>
-  <si>
-    <t>NEWS2 Score</t>
-  </si>
-  <si>
-    <t>ONC Observation Codes#news2-score</t>
-  </si>
-  <si>
-    <t>onc-news2-subscore</t>
-  </si>
-  <si>
-    <t>NEWS2 Sub-Score</t>
-  </si>
-  <si>
-    <t>ONC Observation Codes#news2-subscore</t>
-  </si>
-  <si>
-    <t>onc-nursing-assessment</t>
-  </si>
-  <si>
-    <t>Open Nursing Core Assessment</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1 (example)</t>
-  </si>
-  <si>
-    <t>onc-nursing-strength</t>
-  </si>
-  <si>
-    <t>ONC Nursing Strength</t>
-  </si>
-  <si>
-    <t>ONC Observation Codes#nursing-strengths</t>
-  </si>
-  <si>
-    <t>CodeableConcept, string</t>
-  </si>
-  <si>
-    <t>onc-oral-care-assessment</t>
-  </si>
-  <si>
-    <t>Oral Care Needs Assessment</t>
-  </si>
-  <si>
-    <t>SNOMED CT#30175009</t>
-  </si>
-  <si>
-    <t>onc-oral-intake-assessment</t>
-  </si>
-  <si>
-    <t>Oral Intake Assessment</t>
-  </si>
-  <si>
-    <t>SNOMED CT#288852001</t>
-  </si>
-  <si>
-    <t>onc-oxygen-saturation</t>
-  </si>
-  <si>
-    <t>Oxygen Saturation</t>
-  </si>
-  <si>
-    <t>LOINC#59408-5</t>
-  </si>
-  <si>
-    <t>onc-pain-assessment</t>
-  </si>
-  <si>
-    <t>Pain Assessment (NRS 0-10)</t>
-  </si>
-  <si>
-    <t>https://opennursingcoreig.com/ValueSet/pain-assessment-code-vs (required)</t>
-  </si>
-  <si>
-    <t>dateTime</t>
-  </si>
-  <si>
-    <t>onc-qsofa</t>
-  </si>
-  <si>
-    <t>qSOFA (Quick SOFA)</t>
-  </si>
-  <si>
-    <t>LOINC#96790-1</t>
-  </si>
-  <si>
-    <t>onc-reasonable-adjustment</t>
-  </si>
-  <si>
-    <t>Reasonable Adjustment</t>
-  </si>
-  <si>
-    <t>ONC Observation Codes#reasonable-adjustment</t>
-  </si>
-  <si>
-    <t>onc-respiration-rate</t>
-  </si>
-  <si>
-    <t>Respiration Rate</t>
-  </si>
-  <si>
-    <t>LOINC#9279-1</t>
-  </si>
-  <si>
-    <t>onc-skin-assessment</t>
-  </si>
-  <si>
-    <t>Skin Integrity Assessment</t>
-  </si>
-  <si>
-    <t>SNOMED CT#711041003</t>
-  </si>
-  <si>
-    <t>onc-skintone-observation</t>
-  </si>
-  <si>
-    <t>Skin Tone Observation</t>
-  </si>
-  <si>
-    <t>LOINC#66555-4</t>
-  </si>
-  <si>
-    <t>onc-swallowing-assessment</t>
-  </si>
-  <si>
-    <t>Swallowing Assessment</t>
-  </si>
-  <si>
-    <t>onc-waterlow-score</t>
-  </si>
-  <si>
-    <t>Waterlow Score</t>
-  </si>
-  <si>
-    <t>ONC Observation Codes#waterlow-score</t>
   </si>
   <si>
     <t>onc-wound-assessment</t>
@@ -1553,13 +1553,13 @@
         <v>46</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>14</v>
@@ -1568,7 +1568,7 @@
         <v>16</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>18</v>
@@ -1582,19 +1582,19 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>14</v>
@@ -1603,7 +1603,7 @@
         <v>16</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>18</v>
@@ -1617,19 +1617,19 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>14</v>
@@ -1638,7 +1638,7 @@
         <v>16</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>18</v>
@@ -1652,28 +1652,28 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>18</v>
@@ -1690,7 +1690,7 @@
         <v>14</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>14</v>
@@ -1699,7 +1699,7 @@
         <v>14</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>14</v>
@@ -1708,7 +1708,7 @@
         <v>14</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>18</v>
@@ -1725,7 +1725,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>14</v>
@@ -1734,7 +1734,7 @@
         <v>14</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>14</v>
@@ -1743,7 +1743,7 @@
         <v>14</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>18</v>
@@ -1757,19 +1757,19 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>14</v>
@@ -1778,7 +1778,7 @@
         <v>16</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>18</v>
@@ -1792,19 +1792,19 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>14</v>
@@ -1813,7 +1813,7 @@
         <v>16</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>18</v>
@@ -1827,28 +1827,28 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>18</v>
@@ -1865,7 +1865,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>14</v>
@@ -1874,7 +1874,7 @@
         <v>14</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>14</v>
@@ -1883,7 +1883,7 @@
         <v>14</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>18</v>
@@ -1900,7 +1900,7 @@
         <v>14</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C30" t="s" s="2">
         <v>14</v>
@@ -1909,7 +1909,7 @@
         <v>14</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>14</v>
@@ -1918,7 +1918,7 @@
         <v>14</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>18</v>
@@ -1935,7 +1935,7 @@
         <v>14</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>14</v>
@@ -1944,7 +1944,7 @@
         <v>14</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>14</v>
@@ -1953,7 +1953,7 @@
         <v>14</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>18</v>
@@ -1970,7 +1970,7 @@
         <v>14</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>14</v>
@@ -1979,7 +1979,7 @@
         <v>14</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>14</v>
@@ -1988,7 +1988,7 @@
         <v>14</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>18</v>
@@ -2002,28 +2002,28 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>69</v>
       </c>
-      <c r="B33" t="s" s="2">
-        <v>70</v>
-      </c>
       <c r="C33" t="s" s="2">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>18</v>
@@ -2037,13 +2037,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>14</v>
@@ -2055,10 +2055,10 @@
         <v>14</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>18</v>
@@ -2093,7 +2093,7 @@
         <v>16</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>18</v>
@@ -2107,28 +2107,28 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>18</v>
@@ -2142,28 +2142,28 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>18</v>
@@ -2177,28 +2177,28 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>18</v>
@@ -2212,28 +2212,28 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>18</v>
@@ -2247,19 +2247,19 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>14</v>
@@ -2268,7 +2268,7 @@
         <v>16</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>18</v>
@@ -2282,28 +2282,28 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F41" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>18</v>
@@ -2320,7 +2320,7 @@
         <v>14</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C42" t="s" s="2">
         <v>14</v>
@@ -2329,7 +2329,7 @@
         <v>14</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="F42" t="s" s="2">
         <v>14</v>
@@ -2338,7 +2338,7 @@
         <v>14</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>18</v>
@@ -2355,7 +2355,7 @@
         <v>14</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C43" t="s" s="2">
         <v>14</v>
@@ -2364,7 +2364,7 @@
         <v>14</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>14</v>
@@ -2373,7 +2373,7 @@
         <v>14</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>18</v>
@@ -2387,28 +2387,28 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>18</v>
@@ -2422,28 +2422,28 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>18</v>
@@ -2460,7 +2460,7 @@
         <v>14</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="C46" t="s" s="2">
         <v>14</v>
@@ -2469,7 +2469,7 @@
         <v>14</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>14</v>
@@ -2478,7 +2478,7 @@
         <v>14</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>18</v>
@@ -2495,7 +2495,7 @@
         <v>14</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="C47" t="s" s="2">
         <v>14</v>
@@ -2504,7 +2504,7 @@
         <v>14</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="F47" t="s" s="2">
         <v>14</v>
@@ -2513,7 +2513,7 @@
         <v>14</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>18</v>
@@ -2530,7 +2530,7 @@
         <v>14</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="C48" t="s" s="2">
         <v>14</v>
@@ -2539,7 +2539,7 @@
         <v>14</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>14</v>
@@ -2548,7 +2548,7 @@
         <v>14</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>18</v>
@@ -2562,10 +2562,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="C49" t="s" s="2">
         <v>14</v>
@@ -2574,16 +2574,16 @@
         <v>14</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>18</v>
@@ -2597,28 +2597,28 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>18</v>
@@ -2632,28 +2632,28 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>18</v>
@@ -2670,7 +2670,7 @@
         <v>14</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="C52" t="s" s="2">
         <v>14</v>
@@ -2679,7 +2679,7 @@
         <v>14</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>14</v>
@@ -2688,7 +2688,7 @@
         <v>14</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>18</v>
@@ -2702,19 +2702,19 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>14</v>
@@ -2723,7 +2723,7 @@
         <v>16</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>18</v>
@@ -2737,19 +2737,19 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>14</v>
@@ -2772,19 +2772,19 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="F55" t="s" s="2">
         <v>14</v>
@@ -2793,7 +2793,7 @@
         <v>16</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>18</v>
@@ -2807,19 +2807,19 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="F56" t="s" s="2">
         <v>14</v>
@@ -2842,19 +2842,19 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="F57" t="s" s="2">
         <v>14</v>
@@ -2863,7 +2863,7 @@
         <v>16</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>18</v>
@@ -2877,28 +2877,28 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>18</v>
@@ -2915,7 +2915,7 @@
         <v>14</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="C59" t="s" s="2">
         <v>14</v>
@@ -2924,7 +2924,7 @@
         <v>14</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F59" t="s" s="2">
         <v>14</v>
@@ -2933,7 +2933,7 @@
         <v>14</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>18</v>
@@ -2947,19 +2947,19 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="F60" t="s" s="2">
         <v>14</v>
@@ -2968,7 +2968,7 @@
         <v>16</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>18</v>
@@ -2982,19 +2982,19 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>14</v>
@@ -3003,7 +3003,7 @@
         <v>16</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>18</v>
@@ -3017,19 +3017,19 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="F62" t="s" s="2">
         <v>14</v>
@@ -3055,7 +3055,7 @@
         <v>14</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="C63" t="s" s="2">
         <v>14</v>
@@ -3064,7 +3064,7 @@
         <v>14</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="F63" t="s" s="2">
         <v>14</v>
@@ -3073,7 +3073,7 @@
         <v>14</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>18</v>
@@ -3090,7 +3090,7 @@
         <v>14</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="C64" t="s" s="2">
         <v>14</v>
@@ -3099,7 +3099,7 @@
         <v>14</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="F64" t="s" s="2">
         <v>14</v>
@@ -3108,7 +3108,7 @@
         <v>14</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>18</v>
@@ -3125,7 +3125,7 @@
         <v>14</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="C65" t="s" s="2">
         <v>14</v>
@@ -3134,7 +3134,7 @@
         <v>14</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="F65" t="s" s="2">
         <v>14</v>
@@ -3143,7 +3143,7 @@
         <v>14</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>18</v>
@@ -3157,28 +3157,28 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>14</v>
+        <v>149</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="F66" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>18</v>
@@ -3192,28 +3192,28 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>14</v>
+        <v>152</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="F67" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>18</v>
@@ -3227,28 +3227,28 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>14</v>
+        <v>155</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>14</v>
+        <v>157</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>18</v>
@@ -3262,19 +3262,19 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="F69" t="s" s="2">
         <v>14</v>
@@ -3283,7 +3283,7 @@
         <v>16</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>18</v>
@@ -3297,19 +3297,19 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="F70" t="s" s="2">
         <v>14</v>
@@ -3332,28 +3332,28 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>142</v>
+        <v>14</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="F71" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>18</v>
@@ -3367,19 +3367,19 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="F72" t="s" s="2">
         <v>14</v>
@@ -3388,7 +3388,7 @@
         <v>16</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>18</v>
@@ -3402,28 +3402,28 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>148</v>
+        <v>14</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="F73" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>17</v>
+        <v>169</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>18</v>
@@ -3440,7 +3440,7 @@
         <v>14</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="C74" t="s" s="2">
         <v>14</v>
@@ -3449,7 +3449,7 @@
         <v>14</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="F74" t="s" s="2">
         <v>14</v>
@@ -3458,7 +3458,7 @@
         <v>14</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>18</v>
@@ -3475,7 +3475,7 @@
         <v>14</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="C75" t="s" s="2">
         <v>14</v>
@@ -3484,7 +3484,7 @@
         <v>14</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="F75" t="s" s="2">
         <v>14</v>
@@ -3493,7 +3493,7 @@
         <v>14</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>18</v>
@@ -3510,7 +3510,7 @@
         <v>14</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="C76" t="s" s="2">
         <v>14</v>
@@ -3519,7 +3519,7 @@
         <v>14</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="F76" t="s" s="2">
         <v>14</v>
@@ -3528,7 +3528,7 @@
         <v>14</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>18</v>
@@ -3542,10 +3542,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C77" t="s" s="2">
         <v>14</v>
@@ -3554,16 +3554,16 @@
         <v>14</v>
       </c>
       <c r="E77" t="s" s="2">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="F77" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>18</v>
@@ -3577,19 +3577,19 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="F78" t="s" s="2">
         <v>14</v>
@@ -3598,7 +3598,7 @@
         <v>16</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>18</v>
@@ -3612,19 +3612,19 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="F79" t="s" s="2">
         <v>14</v>
@@ -3633,7 +3633,7 @@
         <v>16</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>18</v>
@@ -3647,28 +3647,28 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>14</v>
+        <v>180</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>163</v>
+        <v>14</v>
       </c>
       <c r="F80" t="s" s="2">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>18</v>
@@ -3682,19 +3682,19 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>75</v>
+        <v>186</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="F81" t="s" s="2">
         <v>14</v>
@@ -3703,7 +3703,7 @@
         <v>16</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>167</v>
+        <v>40</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>18</v>
@@ -3717,19 +3717,19 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D82" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="F82" t="s" s="2">
         <v>14</v>
@@ -3738,7 +3738,7 @@
         <v>16</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>18</v>
@@ -3752,19 +3752,19 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D83" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="F83" t="s" s="2">
         <v>14</v>
@@ -3773,7 +3773,7 @@
         <v>16</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>18</v>
@@ -3787,19 +3787,19 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E84" t="s" s="2">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="F84" t="s" s="2">
         <v>14</v>
@@ -3808,7 +3808,7 @@
         <v>16</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>18</v>
@@ -3822,19 +3822,19 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="F85" t="s" s="2">
         <v>14</v>
@@ -3843,7 +3843,7 @@
         <v>16</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>18</v>
@@ -3857,28 +3857,28 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>14</v>
+        <v>200</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E86" t="s" s="2">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="F86" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>18</v>
@@ -3892,28 +3892,28 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>180</v>
+        <v>14</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="F87" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>38</v>
+        <v>169</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>18</v>
@@ -3927,28 +3927,28 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>183</v>
+        <v>14</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="F88" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>18</v>
@@ -3962,28 +3962,28 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>186</v>
+        <v>14</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E89" t="s" s="2">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="F89" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>17</v>
+        <v>169</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>18</v>
@@ -4000,7 +4000,7 @@
         <v>14</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="C90" t="s" s="2">
         <v>14</v>
@@ -4009,7 +4009,7 @@
         <v>14</v>
       </c>
       <c r="E90" t="s" s="2">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="F90" t="s" s="2">
         <v>14</v>
@@ -4018,7 +4018,7 @@
         <v>14</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>18</v>
@@ -4032,28 +4032,28 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>14</v>
+        <v>207</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="F91" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>18</v>
@@ -4067,28 +4067,28 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>14</v>
+        <v>210</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D92" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E92" t="s" s="2">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="F92" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>18</v>
@@ -4102,19 +4102,19 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="F93" t="s" s="2">
         <v>14</v>
@@ -4123,7 +4123,7 @@
         <v>16</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>18</v>
@@ -4137,28 +4137,28 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>195</v>
+        <v>14</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E94" t="s" s="2">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="F94" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>17</v>
+        <v>169</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>18</v>
@@ -4172,28 +4172,28 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>198</v>
+        <v>14</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E95" t="s" s="2">
-        <v>14</v>
+        <v>217</v>
       </c>
       <c r="F95" t="s" s="2">
-        <v>200</v>
+        <v>14</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>117</v>
+        <v>60</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>18</v>
@@ -4207,10 +4207,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>201</v>
+        <v>14</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="C96" t="s" s="2">
         <v>14</v>
@@ -4219,16 +4219,16 @@
         <v>14</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="F96" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>18</v>
@@ -4242,19 +4242,19 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="F97" t="s" s="2">
         <v>14</v>
@@ -4277,28 +4277,28 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>14</v>
+        <v>221</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E98" t="s" s="2">
-        <v>163</v>
+        <v>223</v>
       </c>
       <c r="F98" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>18</v>
@@ -4312,28 +4312,28 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E99" t="s" s="2">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="F99" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>38</v>
+        <v>169</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>18</v>
@@ -4347,28 +4347,28 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>211</v>
+        <v>14</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E100" t="s" s="2">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="F100" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>17</v>
+        <v>169</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>18</v>
@@ -4382,28 +4382,28 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>214</v>
+        <v>14</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>14</v>
+        <v>226</v>
       </c>
       <c r="F101" t="s" s="2">
-        <v>216</v>
+        <v>14</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>17</v>
+        <v>169</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>18</v>
@@ -4417,28 +4417,28 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>218</v>
+        <v>14</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="F102" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>17</v>
+        <v>169</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>18</v>
@@ -4452,28 +4452,28 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>222</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F103" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>40</v>
+        <v>169</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>18</v>
@@ -4487,28 +4487,28 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>224</v>
+        <v>14</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F104" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>17</v>
+        <v>169</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>18</v>
@@ -4522,28 +4522,28 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>227</v>
+        <v>14</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E105" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F105" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>18</v>
@@ -4557,28 +4557,28 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>230</v>
+        <v>14</v>
       </c>
       <c r="B106" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="C106" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D106" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E106" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="C106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="D106" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E106" t="s" s="2">
-        <v>232</v>
-      </c>
       <c r="F106" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>18</v>
@@ -4592,20 +4592,20 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B107" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="B107" t="s" s="2">
+      <c r="C107" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="D107" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E107" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="C107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="D107" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E107" t="s" s="2">
-        <v>207</v>
-      </c>
       <c r="F107" t="s" s="2">
         <v>14</v>
       </c>
@@ -4613,7 +4613,7 @@
         <v>16</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>18</v>
@@ -4633,7 +4633,7 @@
         <v>236</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>75</v>
+        <v>186</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>14</v>
@@ -4648,7 +4648,7 @@
         <v>16</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>18</v>
@@ -4668,7 +4668,7 @@
         <v>239</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>14</v>
@@ -4718,7 +4718,7 @@
         <v>14</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>18</v>
@@ -4753,7 +4753,7 @@
         <v>14</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>18</v>
@@ -4788,7 +4788,7 @@
         <v>14</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>18</v>

--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -647,7 +647,7 @@
     <t>onc-skintone-observation</t>
   </si>
   <si>
-    <t>Skin Tone Observation</t>
+    <t>Skin Tone Observation (Fitzpatrick -- secondary/legacy)</t>
   </si>
   <si>
     <t>LOINC#66555-4</t>

--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="243">
   <si>
     <t>Profile</t>
   </si>
@@ -92,7 +92,7 @@
     <t>Abbey Pain Scale</t>
   </si>
   <si>
-    <t>Observation Category Codes#exam, Observation Category Codes#survey</t>
+    <t>Observation Category Codes#survey</t>
   </si>
   <si>
     <t>ONC Observation Codes#abbey-score</t>
@@ -153,9 +153,6 @@
   </si>
   <si>
     <t>ACVPU Consciousness Level</t>
-  </si>
-  <si>
-    <t>Observation Category Codes#survey</t>
   </si>
   <si>
     <t>SNOMED CT#1104441000000107</t>
@@ -1553,13 +1550,13 @@
         <v>46</v>
       </c>
       <c r="C20" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E20" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E20" t="s" s="2">
-        <v>48</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>14</v>
@@ -1582,19 +1579,19 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="B21" t="s" s="2">
+      <c r="C21" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E21" t="s" s="2">
         <v>50</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D21" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E21" t="s" s="2">
-        <v>51</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>14</v>
@@ -1617,19 +1614,19 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="B22" t="s" s="2">
+      <c r="C22" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E22" t="s" s="2">
         <v>53</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D22" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E22" t="s" s="2">
-        <v>54</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>14</v>
@@ -1652,28 +1649,28 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="B23" t="s" s="2">
+      <c r="C23" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E23" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="C23" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D23" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E23" t="s" s="2">
+      <c r="F23" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H23" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="F23" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G23" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H23" t="s" s="2">
-        <v>58</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>18</v>
@@ -1690,7 +1687,7 @@
         <v>14</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>14</v>
@@ -1699,16 +1696,16 @@
         <v>14</v>
       </c>
       <c r="E24" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H24" t="s" s="2">
         <v>59</v>
-      </c>
-      <c r="F24" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G24" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="H24" t="s" s="2">
-        <v>60</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>18</v>
@@ -1725,7 +1722,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>14</v>
@@ -1734,7 +1731,7 @@
         <v>14</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>14</v>
@@ -1743,7 +1740,7 @@
         <v>14</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>18</v>
@@ -1757,19 +1754,19 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="B26" t="s" s="2">
+      <c r="C26" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E26" t="s" s="2">
         <v>63</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D26" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E26" t="s" s="2">
-        <v>64</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>14</v>
@@ -1792,19 +1789,19 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>65</v>
       </c>
-      <c r="B27" t="s" s="2">
+      <c r="C27" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E27" t="s" s="2">
         <v>66</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D27" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E27" t="s" s="2">
-        <v>67</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>14</v>
@@ -1827,19 +1824,19 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="B28" t="s" s="2">
+      <c r="C28" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E28" t="s" s="2">
         <v>69</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D28" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E28" t="s" s="2">
-        <v>70</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>14</v>
@@ -1865,7 +1862,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>14</v>
@@ -1874,7 +1871,7 @@
         <v>14</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>14</v>
@@ -1883,7 +1880,7 @@
         <v>14</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>18</v>
@@ -1900,7 +1897,7 @@
         <v>14</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C30" t="s" s="2">
         <v>14</v>
@@ -1909,7 +1906,7 @@
         <v>14</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>14</v>
@@ -1918,7 +1915,7 @@
         <v>14</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>18</v>
@@ -1935,7 +1932,7 @@
         <v>14</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>14</v>
@@ -1944,7 +1941,7 @@
         <v>14</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>14</v>
@@ -1953,7 +1950,7 @@
         <v>14</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>18</v>
@@ -1970,7 +1967,7 @@
         <v>14</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>14</v>
@@ -1979,7 +1976,7 @@
         <v>14</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>14</v>
@@ -1988,7 +1985,7 @@
         <v>14</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>18</v>
@@ -2005,7 +2002,7 @@
         <v>14</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>14</v>
@@ -2014,7 +2011,7 @@
         <v>14</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>14</v>
@@ -2023,7 +2020,7 @@
         <v>14</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>18</v>
@@ -2040,7 +2037,7 @@
         <v>14</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>14</v>
@@ -2049,7 +2046,7 @@
         <v>14</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>14</v>
@@ -2058,7 +2055,7 @@
         <v>14</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>18</v>
@@ -2072,10 +2069,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>77</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>26</v>
@@ -2084,7 +2081,7 @@
         <v>14</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>14</v>
@@ -2107,28 +2104,28 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="B36" t="s" s="2">
+      <c r="C36" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E36" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="C36" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D36" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E36" t="s" s="2">
+      <c r="F36" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H36" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="F36" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G36" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>18</v>
@@ -2142,10 +2139,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="C37" t="s" s="2">
         <v>13</v>
@@ -2154,7 +2151,7 @@
         <v>14</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>14</v>
@@ -2177,19 +2174,19 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="B38" t="s" s="2">
+      <c r="C38" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E38" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D38" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E38" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>14</v>
@@ -2212,20 +2209,20 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="B39" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="B39" t="s" s="2">
+      <c r="C39" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E39" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="C39" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D39" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E39" t="s" s="2">
-        <v>92</v>
-      </c>
       <c r="F39" t="s" s="2">
         <v>14</v>
       </c>
@@ -2233,7 +2230,7 @@
         <v>16</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>18</v>
@@ -2247,19 +2244,19 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="B40" t="s" s="2">
+      <c r="C40" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E40" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D40" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E40" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>14</v>
@@ -2282,10 +2279,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B41" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="C41" t="s" s="2">
         <v>26</v>
@@ -2294,7 +2291,7 @@
         <v>14</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F41" t="s" s="2">
         <v>14</v>
@@ -2320,7 +2317,7 @@
         <v>14</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C42" t="s" s="2">
         <v>14</v>
@@ -2329,7 +2326,7 @@
         <v>14</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F42" t="s" s="2">
         <v>14</v>
@@ -2355,7 +2352,7 @@
         <v>14</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C43" t="s" s="2">
         <v>14</v>
@@ -2364,7 +2361,7 @@
         <v>14</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>14</v>
@@ -2390,7 +2387,7 @@
         <v>14</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C44" t="s" s="2">
         <v>14</v>
@@ -2399,7 +2396,7 @@
         <v>14</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>14</v>
@@ -2422,19 +2419,19 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="B45" t="s" s="2">
+      <c r="C45" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D45" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E45" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D45" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E45" t="s" s="2">
-        <v>104</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>14</v>
@@ -2460,7 +2457,7 @@
         <v>14</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C46" t="s" s="2">
         <v>14</v>
@@ -2469,7 +2466,7 @@
         <v>14</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>14</v>
@@ -2478,7 +2475,7 @@
         <v>14</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>18</v>
@@ -2495,7 +2492,7 @@
         <v>14</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C47" t="s" s="2">
         <v>14</v>
@@ -2504,7 +2501,7 @@
         <v>14</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F47" t="s" s="2">
         <v>14</v>
@@ -2513,7 +2510,7 @@
         <v>14</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>18</v>
@@ -2530,7 +2527,7 @@
         <v>14</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C48" t="s" s="2">
         <v>14</v>
@@ -2539,7 +2536,7 @@
         <v>14</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>14</v>
@@ -2548,7 +2545,7 @@
         <v>14</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>18</v>
@@ -2562,19 +2559,19 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="B49" t="s" s="2">
+      <c r="C49" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D49" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E49" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D49" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E49" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>14</v>
@@ -2597,19 +2594,19 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="B50" t="s" s="2">
+      <c r="C50" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D50" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E50" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D50" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E50" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>14</v>
@@ -2632,19 +2629,19 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="B51" t="s" s="2">
+      <c r="C51" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D51" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E51" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D51" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E51" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>14</v>
@@ -2670,7 +2667,7 @@
         <v>14</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C52" t="s" s="2">
         <v>14</v>
@@ -2679,7 +2676,7 @@
         <v>14</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>14</v>
@@ -2702,28 +2699,28 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="B53" t="s" s="2">
+      <c r="C53" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D53" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E53" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="C53" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D53" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E53" t="s" s="2">
+      <c r="F53" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H53" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="F53" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>18</v>
@@ -2737,19 +2734,19 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="B54" t="s" s="2">
+      <c r="C54" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D54" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E54" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D54" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E54" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>14</v>
@@ -2772,19 +2769,19 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="B55" t="s" s="2">
+      <c r="C55" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E55" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D55" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E55" t="s" s="2">
-        <v>127</v>
       </c>
       <c r="F55" t="s" s="2">
         <v>14</v>
@@ -2807,10 +2804,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="B56" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="C56" t="s" s="2">
         <v>26</v>
@@ -2819,7 +2816,7 @@
         <v>14</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F56" t="s" s="2">
         <v>14</v>
@@ -2842,19 +2839,19 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B57" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="B57" t="s" s="2">
+      <c r="C57" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D57" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E57" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D57" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E57" t="s" s="2">
-        <v>133</v>
       </c>
       <c r="F57" t="s" s="2">
         <v>14</v>
@@ -2877,19 +2874,19 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="B58" t="s" s="2">
+      <c r="C58" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D58" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E58" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D58" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E58" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>14</v>
@@ -2915,7 +2912,7 @@
         <v>14</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C59" t="s" s="2">
         <v>14</v>
@@ -2924,7 +2921,7 @@
         <v>14</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F59" t="s" s="2">
         <v>14</v>
@@ -2947,19 +2944,19 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="B60" t="s" s="2">
+      <c r="C60" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D60" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E60" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D60" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E60" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="F60" t="s" s="2">
         <v>14</v>
@@ -2982,19 +2979,19 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="B61" t="s" s="2">
+      <c r="C61" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D61" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E61" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D61" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E61" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>14</v>
@@ -3017,19 +3014,19 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="B62" t="s" s="2">
+      <c r="C62" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D62" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E62" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D62" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E62" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="F62" t="s" s="2">
         <v>14</v>
@@ -3055,7 +3052,7 @@
         <v>14</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C63" t="s" s="2">
         <v>14</v>
@@ -3064,7 +3061,7 @@
         <v>14</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F63" t="s" s="2">
         <v>14</v>
@@ -3073,7 +3070,7 @@
         <v>14</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>18</v>
@@ -3090,7 +3087,7 @@
         <v>14</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C64" t="s" s="2">
         <v>14</v>
@@ -3099,7 +3096,7 @@
         <v>14</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F64" t="s" s="2">
         <v>14</v>
@@ -3108,7 +3105,7 @@
         <v>14</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>18</v>
@@ -3125,7 +3122,7 @@
         <v>14</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C65" t="s" s="2">
         <v>14</v>
@@ -3134,7 +3131,7 @@
         <v>14</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F65" t="s" s="2">
         <v>14</v>
@@ -3143,7 +3140,7 @@
         <v>14</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>18</v>
@@ -3157,19 +3154,19 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="B66" t="s" s="2">
+      <c r="C66" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D66" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E66" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D66" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E66" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="F66" t="s" s="2">
         <v>14</v>
@@ -3192,19 +3189,19 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="B67" t="s" s="2">
+      <c r="C67" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D67" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E67" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D67" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E67" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="F67" t="s" s="2">
         <v>14</v>
@@ -3227,28 +3224,28 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="B68" t="s" s="2">
+      <c r="C68" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D68" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E68" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F68" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="C68" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D68" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E68" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F68" t="s" s="2">
-        <v>157</v>
-      </c>
       <c r="G68" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>18</v>
@@ -3262,28 +3259,28 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="B69" t="s" s="2">
+      <c r="C69" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D69" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E69" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="C69" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D69" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E69" t="s" s="2">
+      <c r="F69" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H69" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="F69" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>18</v>
@@ -3297,19 +3294,19 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="B70" t="s" s="2">
+      <c r="C70" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D70" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E70" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="C70" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D70" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E70" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="F70" t="s" s="2">
         <v>14</v>
@@ -3335,7 +3332,7 @@
         <v>14</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C71" t="s" s="2">
         <v>14</v>
@@ -3344,7 +3341,7 @@
         <v>14</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F71" t="s" s="2">
         <v>14</v>
@@ -3367,10 +3364,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="C72" t="s" s="2">
         <v>26</v>
@@ -3379,7 +3376,7 @@
         <v>14</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F72" t="s" s="2">
         <v>14</v>
@@ -3405,7 +3402,7 @@
         <v>14</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C73" t="s" s="2">
         <v>14</v>
@@ -3414,16 +3411,16 @@
         <v>14</v>
       </c>
       <c r="E73" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="F73" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H73" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="F73" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>169</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>18</v>
@@ -3440,7 +3437,7 @@
         <v>14</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C74" t="s" s="2">
         <v>14</v>
@@ -3449,7 +3446,7 @@
         <v>14</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F74" t="s" s="2">
         <v>14</v>
@@ -3458,7 +3455,7 @@
         <v>14</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>18</v>
@@ -3475,7 +3472,7 @@
         <v>14</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C75" t="s" s="2">
         <v>14</v>
@@ -3484,7 +3481,7 @@
         <v>14</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F75" t="s" s="2">
         <v>14</v>
@@ -3493,7 +3490,7 @@
         <v>14</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>18</v>
@@ -3510,7 +3507,7 @@
         <v>14</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C76" t="s" s="2">
         <v>14</v>
@@ -3519,7 +3516,7 @@
         <v>14</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F76" t="s" s="2">
         <v>14</v>
@@ -3528,7 +3525,7 @@
         <v>14</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>18</v>
@@ -3545,7 +3542,7 @@
         <v>14</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C77" t="s" s="2">
         <v>14</v>
@@ -3554,7 +3551,7 @@
         <v>14</v>
       </c>
       <c r="E77" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F77" t="s" s="2">
         <v>14</v>
@@ -3563,7 +3560,7 @@
         <v>14</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>18</v>
@@ -3577,19 +3574,19 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="B78" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="B78" t="s" s="2">
+      <c r="C78" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D78" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E78" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D78" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E78" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="F78" t="s" s="2">
         <v>14</v>
@@ -3612,19 +3609,19 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B79" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="B79" t="s" s="2">
+      <c r="C79" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D79" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E79" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D79" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E79" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="F79" t="s" s="2">
         <v>14</v>
@@ -3647,25 +3644,25 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B80" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="B80" t="s" s="2">
+      <c r="C80" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D80" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E80" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F80" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="C80" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D80" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E80" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F80" t="s" s="2">
+      <c r="G80" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>17</v>
@@ -3682,19 +3679,19 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B81" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="B81" t="s" s="2">
+      <c r="C81" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="C81" t="s" s="2">
+      <c r="D81" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E81" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="D81" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E81" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="F81" t="s" s="2">
         <v>14</v>
@@ -3717,19 +3714,19 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B82" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="B82" t="s" s="2">
+      <c r="C82" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D82" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E82" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="C82" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D82" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E82" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="F82" t="s" s="2">
         <v>14</v>
@@ -3752,19 +3749,19 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="B83" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="B83" t="s" s="2">
+      <c r="C83" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D83" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E83" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="C83" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D83" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E83" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="F83" t="s" s="2">
         <v>14</v>
@@ -3787,19 +3784,19 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B84" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="B84" t="s" s="2">
+      <c r="C84" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D84" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E84" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="C84" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D84" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E84" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="F84" t="s" s="2">
         <v>14</v>
@@ -3822,19 +3819,19 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="B85" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="B85" t="s" s="2">
+      <c r="C85" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D85" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E85" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="C85" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D85" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E85" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="F85" t="s" s="2">
         <v>14</v>
@@ -3857,10 +3854,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B86" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="C86" t="s" s="2">
         <v>26</v>
@@ -3869,7 +3866,7 @@
         <v>14</v>
       </c>
       <c r="E86" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F86" t="s" s="2">
         <v>14</v>
@@ -3895,7 +3892,7 @@
         <v>14</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C87" t="s" s="2">
         <v>14</v>
@@ -3904,7 +3901,7 @@
         <v>14</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F87" t="s" s="2">
         <v>14</v>
@@ -3913,7 +3910,7 @@
         <v>14</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>18</v>
@@ -3930,7 +3927,7 @@
         <v>14</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C88" t="s" s="2">
         <v>14</v>
@@ -3939,7 +3936,7 @@
         <v>14</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F88" t="s" s="2">
         <v>14</v>
@@ -3948,7 +3945,7 @@
         <v>14</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>18</v>
@@ -3965,7 +3962,7 @@
         <v>14</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C89" t="s" s="2">
         <v>14</v>
@@ -3974,7 +3971,7 @@
         <v>14</v>
       </c>
       <c r="E89" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F89" t="s" s="2">
         <v>14</v>
@@ -3983,7 +3980,7 @@
         <v>14</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>18</v>
@@ -4000,7 +3997,7 @@
         <v>14</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C90" t="s" s="2">
         <v>14</v>
@@ -4009,7 +4006,7 @@
         <v>14</v>
       </c>
       <c r="E90" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F90" t="s" s="2">
         <v>14</v>
@@ -4018,7 +4015,7 @@
         <v>14</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>18</v>
@@ -4032,19 +4029,19 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="B91" t="s" s="2">
+      <c r="C91" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D91" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E91" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="C91" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D91" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E91" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="F91" t="s" s="2">
         <v>14</v>
@@ -4067,19 +4064,19 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="B92" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="B92" t="s" s="2">
+      <c r="C92" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D92" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E92" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="C92" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D92" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E92" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="F92" t="s" s="2">
         <v>14</v>
@@ -4102,10 +4099,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="B93" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="C93" t="s" s="2">
         <v>26</v>
@@ -4114,7 +4111,7 @@
         <v>14</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F93" t="s" s="2">
         <v>14</v>
@@ -4140,7 +4137,7 @@
         <v>14</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C94" t="s" s="2">
         <v>14</v>
@@ -4149,7 +4146,7 @@
         <v>14</v>
       </c>
       <c r="E94" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F94" t="s" s="2">
         <v>14</v>
@@ -4158,7 +4155,7 @@
         <v>14</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>18</v>
@@ -4175,7 +4172,7 @@
         <v>14</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C95" t="s" s="2">
         <v>14</v>
@@ -4184,7 +4181,7 @@
         <v>14</v>
       </c>
       <c r="E95" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F95" t="s" s="2">
         <v>14</v>
@@ -4193,7 +4190,7 @@
         <v>14</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>18</v>
@@ -4210,7 +4207,7 @@
         <v>14</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C96" t="s" s="2">
         <v>14</v>
@@ -4219,7 +4216,7 @@
         <v>14</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F96" t="s" s="2">
         <v>14</v>
@@ -4228,7 +4225,7 @@
         <v>14</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>18</v>
@@ -4242,19 +4239,19 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="B97" t="s" s="2">
-        <v>220</v>
-      </c>
       <c r="C97" t="s" s="2">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F97" t="s" s="2">
         <v>14</v>
@@ -4277,10 +4274,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="C98" t="s" s="2">
         <v>26</v>
@@ -4289,7 +4286,7 @@
         <v>14</v>
       </c>
       <c r="E98" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F98" t="s" s="2">
         <v>14</v>
@@ -4315,7 +4312,7 @@
         <v>14</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C99" t="s" s="2">
         <v>14</v>
@@ -4324,7 +4321,7 @@
         <v>14</v>
       </c>
       <c r="E99" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F99" t="s" s="2">
         <v>14</v>
@@ -4333,7 +4330,7 @@
         <v>14</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>18</v>
@@ -4350,7 +4347,7 @@
         <v>14</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C100" t="s" s="2">
         <v>14</v>
@@ -4359,7 +4356,7 @@
         <v>14</v>
       </c>
       <c r="E100" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F100" t="s" s="2">
         <v>14</v>
@@ -4368,7 +4365,7 @@
         <v>14</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>18</v>
@@ -4385,7 +4382,7 @@
         <v>14</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C101" t="s" s="2">
         <v>14</v>
@@ -4394,7 +4391,7 @@
         <v>14</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F101" t="s" s="2">
         <v>14</v>
@@ -4403,7 +4400,7 @@
         <v>14</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>18</v>
@@ -4420,7 +4417,7 @@
         <v>14</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C102" t="s" s="2">
         <v>14</v>
@@ -4429,7 +4426,7 @@
         <v>14</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F102" t="s" s="2">
         <v>14</v>
@@ -4438,7 +4435,7 @@
         <v>14</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>18</v>
@@ -4455,7 +4452,7 @@
         <v>14</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C103" t="s" s="2">
         <v>14</v>
@@ -4464,7 +4461,7 @@
         <v>14</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F103" t="s" s="2">
         <v>14</v>
@@ -4473,7 +4470,7 @@
         <v>14</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>18</v>
@@ -4490,7 +4487,7 @@
         <v>14</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C104" t="s" s="2">
         <v>14</v>
@@ -4499,7 +4496,7 @@
         <v>14</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F104" t="s" s="2">
         <v>14</v>
@@ -4508,7 +4505,7 @@
         <v>14</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>18</v>
@@ -4525,7 +4522,7 @@
         <v>14</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C105" t="s" s="2">
         <v>14</v>
@@ -4534,7 +4531,7 @@
         <v>14</v>
       </c>
       <c r="E105" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F105" t="s" s="2">
         <v>14</v>
@@ -4543,7 +4540,7 @@
         <v>14</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>18</v>
@@ -4560,7 +4557,7 @@
         <v>14</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C106" t="s" s="2">
         <v>14</v>
@@ -4569,7 +4566,7 @@
         <v>14</v>
       </c>
       <c r="E106" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F106" t="s" s="2">
         <v>14</v>
@@ -4578,7 +4575,7 @@
         <v>14</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>18</v>
@@ -4592,19 +4589,19 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="B107" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="B107" t="s" s="2">
+      <c r="C107" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D107" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E107" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="C107" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D107" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E107" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="F107" t="s" s="2">
         <v>14</v>
@@ -4627,19 +4624,19 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="B108" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="B108" t="s" s="2">
+      <c r="C108" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="D108" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E108" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="D108" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E108" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="F108" t="s" s="2">
         <v>14</v>
@@ -4662,19 +4659,19 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B109" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="B109" t="s" s="2">
+      <c r="C109" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="D109" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E109" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="C109" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D109" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E109" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="F109" t="s" s="2">
         <v>14</v>
@@ -4700,7 +4697,7 @@
         <v>14</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C110" t="s" s="2">
         <v>14</v>
@@ -4709,7 +4706,7 @@
         <v>14</v>
       </c>
       <c r="E110" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F110" t="s" s="2">
         <v>14</v>
@@ -4718,7 +4715,7 @@
         <v>14</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>18</v>
@@ -4735,7 +4732,7 @@
         <v>14</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C111" t="s" s="2">
         <v>14</v>
@@ -4744,7 +4741,7 @@
         <v>14</v>
       </c>
       <c r="E111" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F111" t="s" s="2">
         <v>14</v>
@@ -4753,7 +4750,7 @@
         <v>14</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>18</v>
@@ -4770,7 +4767,7 @@
         <v>14</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C112" t="s" s="2">
         <v>14</v>
@@ -4779,7 +4776,7 @@
         <v>14</v>
       </c>
       <c r="E112" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F112" t="s" s="2">
         <v>14</v>
@@ -4788,7 +4785,7 @@
         <v>14</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>18</v>
